--- a/02_DIA_inicio_2026_analisis_assets/rbd_9710_escuela-basica-santa-adriana_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9710_escuela-basica-santa-adriana_nt1_rubricas.xlsx
@@ -1932,13 +1932,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9343CED4-1B88-4AA1-B975-270CFAEE04D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6C723D4-429C-4E70-8A3B-6CA33224ADE6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD5915B4-75CE-45DA-A55A-526961A8FDC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA905108-490B-468B-A973-5A1DB17B6841}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A0C29DC-7A71-42A3-8A4A-6F3C7AF955B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6C4B52-C024-4631-9777-D4EEAAE14BAF}"/>
 </file>